--- a/data/trans_dic/P1806_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,67</t>
+          <t>2,23; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,12</t>
+          <t>4,29; 7,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,88</t>
+          <t>3,57; 6,24</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,28</t>
+          <t>2,12; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,58</t>
+          <t>5,03; 9,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,56</t>
+          <t>3,82; 6,43</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,92</t>
+          <t>0,19; 1,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 11,06</t>
+          <t>5,11; 11,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,56</t>
+          <t>0,96; 3,58</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,3</t>
+          <t>1,45; 3,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,46</t>
+          <t>1,97; 5,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,92</t>
+          <t>2,04; 3,9</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,62</t>
+          <t>0,65; 2,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,78</t>
+          <t>3,23; 5,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,28</t>
+          <t>2,57; 4,26</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,82</t>
+          <t>0,95; 8,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,34</t>
+          <t>2,85; 5,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,35</t>
+          <t>2,61; 5,16</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,87</t>
+          <t>1,66; 2,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,48</t>
+          <t>3,94; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,05</t>
+          <t>3,03; 4,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10723; 28631</t>
+          <t>11255; 27634</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18632; 36338</t>
+          <t>19191; 35519</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33401; 56004</t>
+          <t>33974; 59421</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9454; 23892</t>
+          <t>9609; 23658</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19167; 36635</t>
+          <t>19230; 36073</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32040; 54760</t>
+          <t>31911; 53663</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1020; 12840</t>
+          <t>1273; 13135</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8559; 18462</t>
+          <t>8532; 19029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7901; 29701</t>
+          <t>8022; 29860</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14583; 34131</t>
+          <t>15035; 35678</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18923; 53326</t>
+          <t>19234; 54382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42076; 78831</t>
+          <t>41002; 78532</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3157; 12434</t>
+          <t>3088; 12052</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26583; 48635</t>
+          <t>27153; 49461</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33652; 56341</t>
+          <t>33862; 56128</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2018; 18799</t>
+          <t>2295; 20107</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21040; 40596</t>
+          <t>21655; 41884</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26780; 53557</t>
+          <t>26180; 51686</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57877; 96786</t>
+          <t>56017; 97437</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139005; 196144</t>
+          <t>140970; 197797</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209788; 281616</t>
+          <t>210981; 280848</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1806_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,47</t>
+          <t>2,02; 5,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,94</t>
+          <t>4,09; 7,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,24</t>
+          <t>3,42; 5,72</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,23</t>
+          <t>2,05; 5,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,43</t>
+          <t>5,42; 9,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,43</t>
+          <t>3,97; 6,53</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,97</t>
+          <t>0,58; 2,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,4</t>
+          <t>4,95; 11,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,58</t>
+          <t>2,02; 4,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,45</t>
+          <t>1,4; 3,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,56</t>
+          <t>3,66; 6,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,9</t>
+          <t>2,67; 4,12</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,54</t>
+          <t>0,51; 2,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,88</t>
+          <t>3,83; 6,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,26</t>
+          <t>2,61; 4,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,36</t>
+          <t>0,72; 8,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,51</t>
+          <t>2,72; 5,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,16</t>
+          <t>2,51; 4,81</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,89</t>
+          <t>1,79; 2,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,53</t>
+          <t>4,58; 5,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,04</t>
+          <t>3,34; 4,16</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>45467</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11255; 27634</t>
+          <t>11127; 29677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19191; 35519</t>
+          <t>19998; 37641</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33974; 59421</t>
+          <t>35566; 59461</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>31022</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>47422</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9609; 23658</t>
+          <t>9927; 26231</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19230; 36073</t>
+          <t>22932; 40851</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31911; 53663</t>
+          <t>36021; 59190</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>20191</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1273; 13135</t>
+          <t>2721; 12382</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8532; 19029</t>
+          <t>9280; 21384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8022; 29860</t>
+          <t>13335; 28449</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61585</t>
+          <t>66174</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15035; 35678</t>
+          <t>15891; 35903</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19234; 54382</t>
+          <t>31530; 51913</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41002; 78532</t>
+          <t>53231; 82134</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>46769</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3088; 12052</t>
+          <t>2896; 11990</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27153; 49461</t>
+          <t>31839; 50735</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33862; 56128</t>
+          <t>36457; 57793</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38040</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2295; 20107</t>
+          <t>1707; 19307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21655; 41884</t>
+          <t>22910; 43708</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26180; 51686</t>
+          <t>27134; 51947</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>78351</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>171949</t>
+          <t>185714</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248124</t>
+          <t>264064</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56017; 97437</t>
+          <t>61757; 97561</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140970; 197797</t>
+          <t>166337; 208538</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>210981; 280848</t>
+          <t>236270; 294700</t>
         </is>
       </c>
     </row>
